--- a/Тест2/250.xlsx
+++ b/Тест2/250.xlsx
@@ -147,16 +147,16 @@
     <t xml:space="preserve">Biologik usulda aerob kultura nima uchun tekshiriladi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kultura narxini aniqlash uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muhit rangini o'zgartirish uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likopcha hajmini hisoblash uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kislorod miqdorini o'lchash uchun</t>
+    <t xml:space="preserve">Kultura narxini aniqlab olish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhit rangini o'zgartirib qo'yish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likopcha hajmini hisoblab chiqish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kislorod miqdorini o'lchab ko'rish uchun</t>
   </si>
   <si>
     <t xml:space="preserve">Begona mikroblar natijani buzmasligi uchun</t>
